--- a/students/hip4.2 نظری.xlsx
+++ b/students/hip4.2 نظری.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
   <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A850ED19-8048-41AD-A9D3-58B06B634849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20730" windowHeight="11760"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -63,12 +64,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -105,16 +106,16 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -124,8 +125,8 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -398,26 +399,26 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H22"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="10.5703125" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" customWidth="1"/>
-    <col min="5" max="5" width="15.42578125" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" customWidth="1"/>
-    <col min="7" max="7" width="41.5703125" customWidth="1"/>
+    <col min="2" max="2" width="10.59765625" customWidth="1"/>
+    <col min="3" max="3" width="12.09765625" customWidth="1"/>
+    <col min="4" max="4" width="11.69921875" customWidth="1"/>
+    <col min="5" max="5" width="15.3984375" customWidth="1"/>
+    <col min="6" max="6" width="14.8984375" customWidth="1"/>
+    <col min="7" max="7" width="41.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -440,7 +441,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>111442</v>
       </c>
@@ -461,25 +462,29 @@
       </c>
       <c r="G2" s="1"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>111443</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="1"/>
+      <c r="E3" s="1">
+        <v>9127405929</v>
+      </c>
+      <c r="F3" s="1">
+        <v>9123416048</v>
+      </c>
       <c r="G3" s="1"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
         <v>111468</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -497,115 +502,187 @@
       <c r="F4" s="2">
         <v>9128815062</v>
       </c>
-      <c r="G4" s="1"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
       <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
